--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="495"/>
+    <workbookView windowWidth="23775" windowHeight="12375" tabRatio="495"/>
   </bookViews>
   <sheets>
     <sheet name="工资" sheetId="40" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>{title}</t>
   </si>
@@ -279,6 +279,9 @@
     <t>{data.realPayAmount}</t>
   </si>
   <si>
+    <t>{total.no}</t>
+  </si>
+  <si>
     <t>{total.typeName}</t>
   </si>
   <si>
@@ -455,7 +458,7 @@
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="179" formatCode="0.0_);[Red]\(0.0\)"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,15 +503,8 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
@@ -898,7 +894,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -937,14 +933,44 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -954,25 +980,10 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -987,21 +998,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1011,20 +1007,9 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -1037,7 +1022,9 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1053,25 +1040,10 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1199,64 +1171,64 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1265,10 +1237,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1277,10 +1249,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1289,10 +1261,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1301,10 +1273,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1313,10 +1285,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1325,33 +1297,33 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1384,105 +1356,99 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1931,299 +1897,301 @@
       <c r="F2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="11"/>
+      <c r="H2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
       <c r="L2" s="28"/>
-      <c r="M2" s="29" t="s">
+      <c r="M2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="30" t="s">
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="30"/>
-      <c r="U2" s="35" t="s">
+      <c r="T2" s="10"/>
+      <c r="U2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="35" t="s">
+      <c r="V2" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="35"/>
+      <c r="W2" s="32"/>
       <c r="X2" s="10" t="s">
         <v>10</v>
       </c>
       <c r="Y2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Z2" s="29" t="s">
+      <c r="Z2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="AA2" s="34"/>
-      <c r="AB2" s="35" t="s">
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="39" t="s">
+      <c r="AC2" s="35" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" ht="39.95" customHeight="1" spans="1:29">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="S3" s="17" t="s">
+      <c r="S3" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="T3" s="36" t="s">
+      <c r="T3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="16"/>
-      <c r="V3" s="32" t="s">
+      <c r="U3" s="14"/>
+      <c r="V3" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="17" t="s">
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="AA3" s="17" t="s">
+      <c r="AA3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AB3" s="16"/>
-      <c r="AC3" s="40"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="36"/>
     </row>
     <row r="4" customHeight="1" spans="1:29">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="18" t="s">
+      <c r="T4" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="18" t="s">
+      <c r="U4" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="V4" s="18" t="s">
+      <c r="V4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="W4" s="18" t="s">
+      <c r="W4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="18" t="s">
+      <c r="X4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Y4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AC4" s="37" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:32">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="G5" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="H5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="I5" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="J5" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="K5" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="L5" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="M5" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="N5" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="O5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="P5" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="R5" s="18" t="s">
+      <c r="Q5" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="R5" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="T5" s="18" t="s">
+      <c r="S5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="U5" s="18" t="s">
+      <c r="T5" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="V5" s="18" t="s">
+      <c r="U5" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="W5" s="18" t="s">
+      <c r="V5" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="X5" s="18" t="s">
+      <c r="W5" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="Y5" s="18" t="s">
+      <c r="X5" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="Z5" s="18" t="s">
+      <c r="Y5" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="AA5" s="18" t="s">
+      <c r="Z5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="AB5" s="18" t="s">
+      <c r="AA5" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="AC5" s="18" t="s">
+      <c r="AB5" s="20" t="s">
         <v>92</v>
+      </c>
+      <c r="AC5" s="38" t="s">
+        <v>93</v>
       </c>
       <c r="AE5"/>
       <c r="AF5"/>
@@ -2231,52 +2199,52 @@
     <row r="6" customHeight="1" spans="1:32">
       <c r="A6" s="21"/>
       <c r="B6" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="23"/>
       <c r="D6" s="24"/>
       <c r="E6" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
       <c r="H6" s="25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
-      <c r="L6" s="33"/>
+      <c r="L6" s="31"/>
       <c r="M6" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N6" s="25"/>
       <c r="O6" s="25"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33" t="s">
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31" t="s">
         <v>98</v>
       </c>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31" t="s">
+        <v>99</v>
+      </c>
       <c r="W6" s="25"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="42"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="39"/>
+      <c r="AC6" s="40"/>
       <c r="AE6"/>
       <c r="AF6"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
@@ -2285,7 +2253,6 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="V2:W2"/>
     <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="U2:U3"/>

--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23775" windowHeight="12375" tabRatio="495"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="495"/>
   </bookViews>
   <sheets>
     <sheet name="工资" sheetId="40" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>{title}</t>
   </si>
@@ -419,6 +419,9 @@
     <t>财务审核：</t>
   </si>
   <si>
+    <t>分管领导审核：</t>
+  </si>
+  <si>
     <t>审定：</t>
   </si>
   <si>
@@ -681,6 +684,13 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -691,13 +701,6 @@
       <color indexed="8"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1428,10 +1431,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1443,6 +1442,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1937,7 +1940,7 @@
       <c r="AB2" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="35" t="s">
+      <c r="AC2" s="34" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2014,7 +2017,7 @@
         <v>35</v>
       </c>
       <c r="AB3" s="14"/>
-      <c r="AC3" s="36"/>
+      <c r="AC3" s="35"/>
     </row>
     <row r="4" customHeight="1" spans="1:29">
       <c r="A4" s="16" t="s">
@@ -2101,7 +2104,7 @@
       <c r="AB4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="AC4" s="37" t="s">
+      <c r="AC4" s="36" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2190,7 +2193,7 @@
       <c r="AB5" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="AC5" s="38" t="s">
+      <c r="AC5" s="37" t="s">
         <v>93</v>
       </c>
       <c r="AE5"/>
@@ -2214,30 +2217,28 @@
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
       <c r="K6" s="25"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="25" t="s">
+      <c r="L6" s="25" t="s">
         <v>97</v>
       </c>
       <c r="N6" s="25"/>
       <c r="O6" s="25"/>
-      <c r="P6" s="31"/>
+      <c r="P6" s="31" t="s">
+        <v>98</v>
+      </c>
       <c r="Q6" s="31"/>
-      <c r="R6" s="31" t="s">
-        <v>98</v>
-      </c>
       <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
+      <c r="T6" s="31" t="s">
+        <v>99</v>
+      </c>
       <c r="U6" s="31"/>
-      <c r="V6" s="31" t="s">
-        <v>99</v>
-      </c>
       <c r="W6" s="25"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="34"/>
-      <c r="Z6" s="34" t="s">
+      <c r="X6" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AA6" s="34"/>
+      <c r="Y6" s="38"/>
+      <c r="AA6" s="38" t="s">
+        <v>101</v>
+      </c>
       <c r="AB6" s="39"/>
       <c r="AC6" s="40"/>
       <c r="AE6"/>

--- a/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
+++ b/snowy-plugin/snowy-plugin-sys/snowy-plugin-sys-func/src/main/resources/GZTemplateOne.xlsx
@@ -413,13 +413,13 @@
     </r>
   </si>
   <si>
+    <t>分管领导审核：</t>
+  </si>
+  <si>
     <t>财务复核：</t>
   </si>
   <si>
     <t>财务审核：</t>
-  </si>
-  <si>
-    <t>分管领导审核：</t>
   </si>
   <si>
     <t>审定：</t>
@@ -684,13 +684,6 @@
       <charset val="0"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -701,6 +694,13 @@
       <color indexed="8"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
